--- a/data/availability/projects/emaar-misr/marassi-red-sea.xlsx
+++ b/data/availability/projects/emaar-misr/marassi-red-sea.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1359,7 +1359,6 @@
       <c r="G2" t="n">
         <v>167.3</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1370,7 +1369,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1416,7 +1415,6 @@
       <c r="G3" t="n">
         <v>120</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1427,7 +1425,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1473,7 +1471,6 @@
       <c r="G4" t="n">
         <v>120</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1484,7 +1481,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1530,7 +1527,6 @@
       <c r="G5" t="n">
         <v>120</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1541,7 +1537,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1587,7 +1583,6 @@
       <c r="G6" t="n">
         <v>679.8</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1598,7 +1593,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1644,7 +1639,6 @@
       <c r="G7" t="n">
         <v>682.6</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1655,7 +1649,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1701,7 +1695,6 @@
       <c r="G8" t="n">
         <v>620.2</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1712,7 +1705,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1758,7 +1751,6 @@
       <c r="G9" t="n">
         <v>698.3</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1769,7 +1761,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1815,7 +1807,6 @@
       <c r="G10" t="n">
         <v>743</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1826,7 +1817,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1872,7 +1863,6 @@
       <c r="G11" t="n">
         <v>697.9</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1883,7 +1873,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1929,7 +1919,6 @@
       <c r="G12" t="n">
         <v>692.7</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1940,7 +1929,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1986,7 +1975,6 @@
       <c r="G13" t="n">
         <v>680.3</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -1997,7 +1985,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2043,7 +2031,6 @@
       <c r="G14" t="n">
         <v>682.1</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2054,7 +2041,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2100,7 +2087,6 @@
       <c r="G15" t="n">
         <v>668.6</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2111,7 +2097,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2157,7 +2143,6 @@
       <c r="G16" t="n">
         <v>654.7</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2168,7 +2153,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2214,7 +2199,6 @@
       <c r="G17" t="n">
         <v>667.8</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2225,7 +2209,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2271,7 +2255,6 @@
       <c r="G18" t="n">
         <v>692.9</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2282,7 +2265,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2328,7 +2311,6 @@
       <c r="G19" t="n">
         <v>556.8</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2339,7 +2321,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2385,7 +2367,6 @@
       <c r="G20" t="n">
         <v>584.2</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2396,7 +2377,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2442,7 +2423,6 @@
       <c r="G21" t="n">
         <v>602.9</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2453,7 +2433,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2499,7 +2479,6 @@
       <c r="G22" t="n">
         <v>667.5</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2510,7 +2489,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2556,7 +2535,6 @@
       <c r="G23" t="n">
         <v>671.3</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2567,7 +2545,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2613,7 +2591,6 @@
       <c r="G24" t="n">
         <v>687.9</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2624,7 +2601,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2670,7 +2647,6 @@
       <c r="G25" t="n">
         <v>696.5</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2681,7 +2657,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2727,7 +2703,6 @@
       <c r="G26" t="n">
         <v>702.3</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2738,7 +2713,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2784,7 +2759,6 @@
       <c r="G27" t="n">
         <v>706.5</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2795,7 +2769,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2841,7 +2815,6 @@
       <c r="G28" t="n">
         <v>708.8</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2852,7 +2825,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2898,7 +2871,6 @@
       <c r="G29" t="n">
         <v>660.8</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2909,7 +2881,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2955,7 +2927,6 @@
       <c r="G30" t="n">
         <v>617.9</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -2966,7 +2937,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3012,7 +2983,6 @@
       <c r="G31" t="n">
         <v>617.2</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3023,7 +2993,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3069,7 +3039,6 @@
       <c r="G32" t="n">
         <v>617.3</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3080,7 +3049,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3126,7 +3095,6 @@
       <c r="G33" t="n">
         <v>617.3</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3137,7 +3105,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3183,7 +3151,6 @@
       <c r="G34" t="n">
         <v>617.2</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3194,7 +3161,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3240,7 +3207,6 @@
       <c r="G35" t="n">
         <v>617.1</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3251,7 +3217,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3297,7 +3263,6 @@
       <c r="G36" t="n">
         <v>599.2</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3308,7 +3273,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3354,7 +3319,6 @@
       <c r="G37" t="n">
         <v>123</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3365,7 +3329,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3411,7 +3375,6 @@
       <c r="G38" t="n">
         <v>692.7</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3422,7 +3385,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3468,7 +3431,6 @@
       <c r="G39" t="n">
         <v>691.6</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3479,7 +3441,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3525,7 +3487,6 @@
       <c r="G40" t="n">
         <v>748.2</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3536,7 +3497,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3582,7 +3543,6 @@
       <c r="G41" t="n">
         <v>860.6</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3593,7 +3553,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3639,7 +3599,6 @@
       <c r="G42" t="n">
         <v>780.9</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3650,7 +3609,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3696,7 +3655,6 @@
       <c r="G43" t="n">
         <v>485.8</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3707,7 +3665,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3753,7 +3711,6 @@
       <c r="G44" t="n">
         <v>468.7</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3764,7 +3721,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3810,7 +3767,6 @@
       <c r="G45" t="n">
         <v>463</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3821,7 +3777,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3867,7 +3823,6 @@
       <c r="G46" t="n">
         <v>485.7</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3878,7 +3833,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3924,7 +3879,6 @@
       <c r="G47" t="n">
         <v>584.5</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3935,7 +3889,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3981,7 +3935,6 @@
       <c r="G48" t="n">
         <v>590.3</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -3992,7 +3945,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4038,7 +3991,6 @@
       <c r="G49" t="n">
         <v>510</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4049,7 +4001,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4095,7 +4047,6 @@
       <c r="G50" t="n">
         <v>493.6</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4106,7 +4057,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4152,7 +4103,6 @@
       <c r="G51" t="n">
         <v>513</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4163,7 +4113,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4209,7 +4159,6 @@
       <c r="G52" t="n">
         <v>514.6</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4220,7 +4169,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4266,7 +4215,6 @@
       <c r="G53" t="n">
         <v>460.8</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4277,7 +4225,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4323,7 +4271,6 @@
       <c r="G54" t="n">
         <v>481.9</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4334,7 +4281,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4380,7 +4327,6 @@
       <c r="G55" t="n">
         <v>523.8</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4391,7 +4337,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>31/03/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4437,7 +4383,6 @@
       <c r="G56" t="n">
         <v>120</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4448,7 +4393,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4494,7 +4439,6 @@
       <c r="G57" t="n">
         <v>120</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4505,7 +4449,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4551,7 +4495,6 @@
       <c r="G58" t="n">
         <v>120</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4562,7 +4505,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4608,7 +4551,6 @@
       <c r="G59" t="n">
         <v>120</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4619,7 +4561,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4665,7 +4607,6 @@
       <c r="G60" t="n">
         <v>120</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4676,7 +4617,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4722,7 +4663,6 @@
       <c r="G61" t="n">
         <v>120</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4733,7 +4673,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4779,7 +4719,6 @@
       <c r="G62" t="n">
         <v>120</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4790,7 +4729,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4836,7 +4775,6 @@
       <c r="G63" t="n">
         <v>120</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4847,7 +4785,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4893,7 +4831,6 @@
       <c r="G64" t="n">
         <v>120</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4904,7 +4841,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4950,7 +4887,6 @@
       <c r="G65" t="n">
         <v>120</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -4961,7 +4897,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5007,7 +4943,6 @@
       <c r="G66" t="n">
         <v>120</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5018,7 +4953,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5064,7 +4999,6 @@
       <c r="G67" t="n">
         <v>120</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5075,7 +5009,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5121,7 +5055,6 @@
       <c r="G68" t="n">
         <v>120</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5132,7 +5065,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5178,7 +5111,6 @@
       <c r="G69" t="n">
         <v>120</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5189,7 +5121,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5235,7 +5167,6 @@
       <c r="G70" t="n">
         <v>120</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5246,7 +5177,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5292,7 +5223,6 @@
       <c r="G71" t="n">
         <v>120</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5303,7 +5233,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5349,7 +5279,6 @@
       <c r="G72" t="n">
         <v>120</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5360,7 +5289,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5406,7 +5335,6 @@
       <c r="G73" t="n">
         <v>120</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5417,7 +5345,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5463,7 +5391,6 @@
       <c r="G74" t="n">
         <v>120</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5474,7 +5401,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5520,7 +5447,6 @@
       <c r="G75" t="n">
         <v>120</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5531,7 +5457,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5577,7 +5503,6 @@
       <c r="G76" t="n">
         <v>120</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5588,7 +5513,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5634,7 +5559,6 @@
       <c r="G77" t="n">
         <v>120</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5645,7 +5569,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5691,7 +5615,6 @@
       <c r="G78" t="n">
         <v>120</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape &amp; Lakes</t>
@@ -5702,7 +5625,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>31/08/2030</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
